--- a/artfynd/A 22057-2025 artfynd.xlsx
+++ b/artfynd/A 22057-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013827</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127013829</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127013828</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127013826</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22057-2025 artfynd.xlsx
+++ b/artfynd/A 22057-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013827</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127013829</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127013828</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127013826</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22057-2025 artfynd.xlsx
+++ b/artfynd/A 22057-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013827</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127013829</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127013828</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127013826</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22057-2025 artfynd.xlsx
+++ b/artfynd/A 22057-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013827</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127013829</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127013828</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127013826</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
